--- a/ckan_batch/src/ckan_batch/reader/templates/PIDINST_Example.xlsx
+++ b/ckan_batch/src/ckan_batch/reader/templates/PIDINST_Example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive_D\projects\avre\apps\PIDINST\AuScope-instrument-registry\ckan_batch\src\ckan_batch\reader\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B29D50-AA81-4EFD-92E0-799103CE51F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4549AE51-768E-4841-8A30-ABAA4CA6F7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30840" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruments" sheetId="1" r:id="rId1"/>
@@ -1011,6 +1011,24 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1020,15 +1038,6 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1081,15 +1090,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1340,7 +1340,7 @@
     <col min="34" max="34" width="20" customWidth="1"/>
     <col min="35" max="37" width="18" customWidth="1"/>
     <col min="38" max="38" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.85546875" customWidth="1"/>
     <col min="40" max="43" width="10.28515625" customWidth="1"/>
     <col min="44" max="44" width="10" customWidth="1"/>
     <col min="45" max="45" width="46.28515625" customWidth="1"/>
@@ -1357,120 +1357,120 @@
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="23"/>
-      <c r="AA2" s="23"/>
-      <c r="AB2" s="23"/>
-      <c r="AC2" s="23"/>
-      <c r="AD2" s="28" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28" t="s">
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
+      <c r="AQ2" s="31"/>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
+      <c r="AT2" s="31"/>
+      <c r="AU2" s="31"/>
+      <c r="AV2" s="31"/>
+      <c r="AW2" s="31"/>
     </row>
     <row r="3" spans="1:49" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="35" t="s">
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="37"/>
-      <c r="AD3" s="41" t="s">
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="AE3" s="42"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="42"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="42"/>
-      <c r="AK3" s="42"/>
-      <c r="AL3" s="42"/>
-      <c r="AM3" s="42"/>
-      <c r="AN3" s="42"/>
-      <c r="AO3" s="42"/>
-      <c r="AP3" s="42"/>
-      <c r="AQ3" s="42"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="26" t="s">
+      <c r="AE3" s="18"/>
+      <c r="AF3" s="18"/>
+      <c r="AG3" s="18"/>
+      <c r="AH3" s="18"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="18"/>
+      <c r="AN3" s="18"/>
+      <c r="AO3" s="18"/>
+      <c r="AP3" s="18"/>
+      <c r="AQ3" s="18"/>
+      <c r="AR3" s="19"/>
+      <c r="AS3" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="AT3" s="27"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
     </row>
     <row r="4" spans="1:49" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -1486,74 +1486,74 @@
       <c r="E4" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="30"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="29" t="s">
+      <c r="G4" s="33"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="J4" s="30"/>
-      <c r="K4" s="31"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="34"/>
       <c r="L4" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="M4" s="21"/>
+      <c r="M4" s="22"/>
       <c r="N4" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="O4" s="22"/>
+      <c r="O4" s="21"/>
       <c r="P4" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="17" t="s">
+      <c r="Q4" s="22"/>
+      <c r="R4" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
-      <c r="V4" s="19"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="25"/>
       <c r="W4" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="21"/>
-      <c r="Z4" s="21"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="22"/>
       <c r="AA4" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="22"/>
-      <c r="AD4" s="32" t="s">
+      <c r="AB4" s="22"/>
+      <c r="AC4" s="21"/>
+      <c r="AD4" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="34"/>
-      <c r="AH4" s="32" t="s">
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="37"/>
+      <c r="AH4" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="AI4" s="34"/>
-      <c r="AJ4" s="32" t="s">
+      <c r="AI4" s="37"/>
+      <c r="AJ4" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="AK4" s="33"/>
-      <c r="AL4" s="33"/>
-      <c r="AM4" s="33"/>
-      <c r="AN4" s="33"/>
-      <c r="AO4" s="33"/>
-      <c r="AP4" s="33"/>
-      <c r="AQ4" s="33"/>
-      <c r="AR4" s="34"/>
-      <c r="AS4" s="24" t="s">
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="37"/>
+      <c r="AS4" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="AT4" s="25"/>
-      <c r="AU4" s="25"/>
-      <c r="AV4" s="25"/>
-      <c r="AW4" s="25"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
     </row>
     <row r="5" spans="1:49" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1668,22 +1668,22 @@
         <v>179</v>
       </c>
       <c r="AL5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM5" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AM5" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="AN5" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="AO5" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="AO5" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="AP5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="AQ5" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="AR5" s="1" t="s">
         <v>19</v>
@@ -1823,16 +1823,16 @@
         <v>174</v>
       </c>
       <c r="AN6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="AO6" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AO6" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="AP6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="AQ6" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="AR6" s="2" t="s">
         <v>44</v>
@@ -2095,12 +2095,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AD3:AR3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:V4"/>
-    <mergeCell ref="W4:Z4"/>
-    <mergeCell ref="AA4:AC4"/>
     <mergeCell ref="A2:AC2"/>
     <mergeCell ref="AS4:AW4"/>
     <mergeCell ref="AS3:AW3"/>
@@ -2114,6 +2108,12 @@
     <mergeCell ref="AJ4:AR4"/>
     <mergeCell ref="L3:AC3"/>
     <mergeCell ref="B3:K3"/>
+    <mergeCell ref="AD3:AR3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:V4"/>
+    <mergeCell ref="W4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -2595,81 +2595,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="9357ce84-a672-4584-8ddb-e5b553dfe263">6KAJUDXX5TY3-1158213377-2347</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="9357ce84-a672-4584-8ddb-e5b553dfe263">
-      <Url>https://csiroau.sharepoint.com/sites/AuScopePortalRefresh/_layouts/15/DocIdRedir.aspx?ID=6KAJUDXX5TY3-1158213377-2347</Url>
-      <Description>6KAJUDXX5TY3-1158213377-2347</Description>
-    </_dlc_DocIdUrl>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f66f598c-5a54-48fa-b12a-3e2e658c8d92">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9357ce84-a672-4584-8ddb-e5b553dfe263" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C458252014B43B48B36D6FD06F31079C" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8411b2fcd13e9c262f801c2de01d8359">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9357ce84-a672-4584-8ddb-e5b553dfe263" xmlns:ns3="f66f598c-5a54-48fa-b12a-3e2e658c8d92" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7559adb2811d00dbbd5f4bbaad764c99" ns2:_="" ns3:_="">
     <xsd:import namespace="9357ce84-a672-4584-8ddb-e5b553dfe263"/>
@@ -2931,34 +2856,82 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E57F81-9D8B-47B3-8107-9966928F030D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9357ce84-a672-4584-8ddb-e5b553dfe263"/>
-    <ds:schemaRef ds:uri="f66f598c-5a54-48fa-b12a-3e2e658c8d92"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B91B4E20-BE34-4CB5-9F97-891AD3D92955}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FB246EF-5385-459E-BC46-E2D2C91CAB60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="9357ce84-a672-4584-8ddb-e5b553dfe263">6KAJUDXX5TY3-1158213377-2347</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="9357ce84-a672-4584-8ddb-e5b553dfe263">
+      <Url>https://csiroau.sharepoint.com/sites/AuScopePortalRefresh/_layouts/15/DocIdRedir.aspx?ID=6KAJUDXX5TY3-1158213377-2347</Url>
+      <Description>6KAJUDXX5TY3-1158213377-2347</Description>
+    </_dlc_DocIdUrl>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f66f598c-5a54-48fa-b12a-3e2e658c8d92">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9357ce84-a672-4584-8ddb-e5b553dfe263" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70706F67-F4D0-436B-9C39-1388BCD46E53}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2975,4 +2948,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FB246EF-5385-459E-BC46-E2D2C91CAB60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B91B4E20-BE34-4CB5-9F97-891AD3D92955}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E57F81-9D8B-47B3-8107-9966928F030D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9357ce84-a672-4584-8ddb-e5b553dfe263"/>
+    <ds:schemaRef ds:uri="f66f598c-5a54-48fa-b12a-3e2e658c8d92"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>